--- a/AAII_Financials/Yearly/ENOV_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/ENOV_YR_FIN.xlsx
@@ -932,13 +932,13 @@
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>1155000</v>
+        <v>1201400</v>
       </c>
       <c r="E14" s="3">
-        <v>825800</v>
+        <v>829300</v>
       </c>
       <c r="F14" s="3">
-        <v>87000</v>
+        <v>93100</v>
       </c>
       <c r="G14" s="3">
         <v>-35000</v>
@@ -1024,13 +1024,13 @@
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>2173300</v>
+        <v>2172700</v>
       </c>
       <c r="E17" s="3">
-        <v>2037400</v>
+        <v>2033900</v>
       </c>
       <c r="F17" s="3">
-        <v>1693200</v>
+        <v>1687100</v>
       </c>
       <c r="G17" s="3">
         <v>1578200</v>
@@ -1063,13 +1063,13 @@
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>74800</v>
+        <v>75400</v>
       </c>
       <c r="E18" s="3">
-        <v>70200</v>
+        <v>73700</v>
       </c>
       <c r="F18" s="3">
-        <v>14000</v>
+        <v>20100</v>
       </c>
       <c r="G18" s="3">
         <v>-15100</v>
@@ -1119,7 +1119,7 @@
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>44400</v>
+        <v>-1400</v>
       </c>
       <c r="E20" s="3">
         <v>10200</v>
@@ -1158,13 +1158,13 @@
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>204000</v>
+        <v>250500</v>
       </c>
       <c r="E21" s="3">
-        <v>225500</v>
+        <v>229000</v>
       </c>
       <c r="F21" s="3">
-        <v>173200</v>
+        <v>179300</v>
       </c>
       <c r="G21" s="3">
         <v>114000</v>
@@ -1587,7 +1587,7 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-44400</v>
+        <v>1400</v>
       </c>
       <c r="E32" s="3">
         <v>-10200</v>
